--- a/Result/profitability/6505.xlsx
+++ b/Result/profitability/6505.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5075000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>4.80375</v>
+        <v>6.69875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8137500000000001</v>
+        <v>1.06875</v>
       </c>
       <c r="N3" t="n">
-        <v>6.32</v>
+        <v>7.8575</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0125</v>
+        <v>1.23625</v>
       </c>
       <c r="N4" t="n">
-        <v>6.842499999999999</v>
+        <v>8.10375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5537500000000001</v>
+        <v>0.925</v>
       </c>
       <c r="N5" t="n">
-        <v>2.890000000000001</v>
+        <v>5.02625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6887500000000001</v>
+        <v>0.84875</v>
       </c>
       <c r="N6" t="n">
-        <v>4.563750000000001</v>
+        <v>5.387500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7450000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.91875</v>
+        <v>5.947500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.85375</v>
+        <v>0.8587500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>5.20375</v>
+        <v>4.8425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>1.08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.7212500000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>4.00875</v>
+        <v>4.008750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7325000000000002</v>
+        <v>0.7325</v>
       </c>
       <c r="N10" t="n">
         <v>3.930000000000001</v>
@@ -1775,7 +1775,7 @@
         <v>0.6012500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>3.355</v>
+        <v>3.355000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>182983</v>
+      </c>
+      <c r="D75" t="n">
+        <v>157553</v>
+      </c>
+      <c r="E75" t="n">
+        <v>25430</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22883</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3086</v>
+      </c>
+      <c r="J75" t="n">
+        <v>25969</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20778</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6475000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.57875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.01869158878504673</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.889999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1721262656343061</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.759493670886076</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-5.357366771159874</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
